--- a/outputs/monitor_xlsx/20260408.xlsx
+++ b/outputs/monitor_xlsx/20260408.xlsx
@@ -536,12 +536,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>33229.82</t>
+          <t>34761.38</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+2.02%</t>
+          <t>+4.61%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -562,12 +562,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>325.61</t>
+          <t>341.2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>+2.43%</t>
+          <t>+4.79%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -640,12 +640,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4736.9$</t>
+          <t>4749.5$</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>+1.71%</t>
+          <t>+1.98%</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -744,12 +744,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>97.02$</t>
+          <t>94.41$</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-14.10%</t>
+          <t>-16.41%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -776,22 +776,22 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-300.06億</t>
+          <t>63.36億</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-1500.3億</t>
+          <t>316.79億</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-328.26億</t>
+          <t>None億</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-6565.17億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>58.66億</t>
+          <t>61.69億</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>293.3億</t>
+          <t>308.43億</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -838,7 +838,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>123.63%</t>
+          <t>141.14%</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -892,7 +892,7 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7958口</t>
+          <t>8317口</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -918,22 +918,22 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6.86億</t>
+          <t>-9.15億</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>34.29億</t>
+          <t>-45.74億</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-7.68億</t>
+          <t>-16.21億</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-153.59億</t>
+          <t>-324.16億</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-300.06億</t>
+          <t>63.36億</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1500.3億</t>
+          <t>316.79億</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-328.26億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-6565.17億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>58.66億</t>
+          <t>61.69億</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>293.3億</t>
+          <t>308.43億</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6.86億</t>
+          <t>-9.15億</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>34.29億</t>
+          <t>-45.74億</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-7.68億</t>
+          <t>-16.21億</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-153.59億</t>
+          <t>-324.16億</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7958口</t>
+          <t>8317口</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W17"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1163,14 +1163,13 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1258,40 +1257,35 @@
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>籌碼評價</t>
+          <t>買賣券商差</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>買賣券商差</t>
+          <t>籌碼集中度5D(%)</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>籌碼集中度5D(%)</t>
+          <t>借券賣出餘額</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>借券賣出餘額</t>
+          <t>短回補天數</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
+          <t>VWAP乖離(%)</t>
         </is>
       </c>
       <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>VWAP乖離(%)</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1326,13 +1320,13 @@
         <v>96385</v>
       </c>
       <c r="H4" t="n">
-        <v>-216268</v>
+        <v>-145526</v>
       </c>
       <c r="I4" t="n">
         <v>-2116</v>
       </c>
       <c r="J4" t="n">
-        <v>6200</v>
+        <v>4300</v>
       </c>
       <c r="K4" t="n">
         <v>9607</v>
@@ -1341,20 +1335,12 @@
         <v>11328</v>
       </c>
       <c r="M4" t="n">
-        <v>68984</v>
+        <v>54578</v>
       </c>
       <c r="N4" t="n">
         <v>-4627719</v>
       </c>
-      <c r="O4" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1389,13 +1375,13 @@
         <v>132</v>
       </c>
       <c r="H5" t="n">
-        <v>2801</v>
+        <v>2498</v>
       </c>
       <c r="I5" t="n">
         <v>-7</v>
       </c>
       <c r="J5" t="n">
-        <v>-1385</v>
+        <v>-948</v>
       </c>
       <c r="K5" t="n">
         <v>13</v>
@@ -1404,20 +1390,12 @@
         <v>2637</v>
       </c>
       <c r="M5" t="n">
-        <v>13530</v>
+        <v>10745</v>
       </c>
       <c r="N5" t="n">
         <v>-78961</v>
       </c>
-      <c r="O5" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1452,13 +1430,13 @@
         <v>3910</v>
       </c>
       <c r="H6" t="n">
-        <v>-4599</v>
+        <v>-3757</v>
       </c>
       <c r="I6" t="n">
         <v>-33</v>
       </c>
       <c r="J6" t="n">
-        <v>916</v>
+        <v>827</v>
       </c>
       <c r="K6" t="n">
         <v>390</v>
@@ -1467,20 +1445,12 @@
         <v>5641</v>
       </c>
       <c r="M6" t="n">
-        <v>26685</v>
+        <v>21078</v>
       </c>
       <c r="N6" t="n">
         <v>-649289</v>
       </c>
-      <c r="O6" t="n">
-        <v>14.28</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1515,13 +1485,13 @@
         <v>18393</v>
       </c>
       <c r="H7" t="n">
-        <v>-33721</v>
+        <v>-17762</v>
       </c>
       <c r="I7" t="n">
         <v>452</v>
       </c>
       <c r="J7" t="n">
-        <v>2840</v>
+        <v>2282</v>
       </c>
       <c r="K7" t="n">
         <v>435</v>
@@ -1530,20 +1500,12 @@
         <v>26797</v>
       </c>
       <c r="M7" t="n">
-        <v>132254</v>
+        <v>105559</v>
       </c>
       <c r="N7" t="n">
         <v>-6483092</v>
       </c>
-      <c r="O7" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1578,13 +1540,13 @@
         <v>-787</v>
       </c>
       <c r="H8" t="n">
-        <v>-1995</v>
+        <v>-1798</v>
       </c>
       <c r="I8" t="n">
         <v>337</v>
       </c>
       <c r="J8" t="n">
-        <v>1879</v>
+        <v>1040</v>
       </c>
       <c r="K8" t="n">
         <v>87</v>
@@ -1593,20 +1555,12 @@
         <v>1777</v>
       </c>
       <c r="M8" t="n">
-        <v>10152</v>
+        <v>7927</v>
       </c>
       <c r="N8" t="n">
         <v>-140279</v>
       </c>
-      <c r="O8" t="n">
-        <v>6.74</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1641,13 +1595,13 @@
         <v>94</v>
       </c>
       <c r="H9" t="n">
-        <v>-234</v>
+        <v>-616</v>
       </c>
       <c r="I9" t="n">
         <v>-9</v>
       </c>
       <c r="J9" t="n">
-        <v>441</v>
+        <v>261</v>
       </c>
       <c r="K9" t="n">
         <v>84</v>
@@ -1656,20 +1610,12 @@
         <v>2340</v>
       </c>
       <c r="M9" t="n">
-        <v>11066</v>
+        <v>8475</v>
       </c>
       <c r="N9" t="n">
         <v>-106305</v>
       </c>
-      <c r="O9" t="n">
-        <v>10.51</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1704,13 +1650,13 @@
         <v>643</v>
       </c>
       <c r="H10" t="n">
-        <v>-509</v>
+        <v>-49</v>
       </c>
       <c r="I10" t="n">
         <v>64</v>
       </c>
       <c r="J10" t="n">
-        <v>512</v>
+        <v>543</v>
       </c>
       <c r="K10" t="n">
         <v>114</v>
@@ -1719,20 +1665,12 @@
         <v>1965</v>
       </c>
       <c r="M10" t="n">
-        <v>9224</v>
+        <v>7339</v>
       </c>
       <c r="N10" t="n">
         <v>-89552</v>
       </c>
-      <c r="O10" t="n">
-        <v>13.91</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1767,13 +1705,13 @@
         <v>-140</v>
       </c>
       <c r="H11" t="n">
-        <v>-179</v>
+        <v>-14</v>
       </c>
       <c r="I11" t="n">
         <v>48</v>
       </c>
       <c r="J11" t="n">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="K11" t="n">
         <v>38</v>
@@ -1782,20 +1720,12 @@
         <v>3879</v>
       </c>
       <c r="M11" t="n">
-        <v>19418</v>
+        <v>15398</v>
       </c>
       <c r="N11" t="n">
         <v>-19405</v>
       </c>
-      <c r="O11" t="n">
-        <v>6.81</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1830,13 +1760,13 @@
         <v>74</v>
       </c>
       <c r="H12" t="n">
-        <v>257</v>
+        <v>219</v>
       </c>
       <c r="I12" t="n">
         <v>-10</v>
       </c>
       <c r="J12" t="n">
-        <v>-370</v>
+        <v>-327</v>
       </c>
       <c r="K12" t="n">
         <v>11</v>
@@ -1845,20 +1775,12 @@
         <v>318</v>
       </c>
       <c r="M12" t="n">
-        <v>1570</v>
+        <v>1274</v>
       </c>
       <c r="N12" t="n">
         <v>-8988</v>
       </c>
-      <c r="O12" t="n">
-        <v>9.02</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1881,25 +1803,25 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2040</v>
+        <v>2315</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>1.75</v>
+        <v>9.98</v>
       </c>
       <c r="F13" t="n">
-        <v>4660</v>
+        <v>2730</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>-189</v>
       </c>
       <c r="H13" t="n">
-        <v>-201</v>
+        <v>-240</v>
       </c>
       <c r="I13" t="n">
         <v>-150</v>
       </c>
       <c r="J13" t="n">
-        <v>1002</v>
+        <v>1032</v>
       </c>
       <c r="K13" t="n">
         <v>-11</v>
@@ -1908,20 +1830,12 @@
         <v>-45</v>
       </c>
       <c r="M13" t="n">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1944,22 +1858,22 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>421.5</v>
+        <v>449.5</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>4.2</v>
+        <v>4.78</v>
       </c>
       <c r="F14" t="n">
-        <v>2041</v>
+        <v>3871</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>-286</v>
       </c>
       <c r="H14" t="n">
-        <v>122</v>
+        <v>383</v>
       </c>
       <c r="J14" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>19</v>
@@ -1968,20 +1882,12 @@
         <v>-96</v>
       </c>
       <c r="M14" t="n">
-        <v>-1292</v>
+        <v>-962</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2004,19 +1910,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>980</v>
+        <v>974</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>6.52</v>
+        <v>9.93</v>
       </c>
       <c r="F15" t="n">
-        <v>784</v>
+        <v>1350</v>
       </c>
       <c r="G15" s="7" t="n">
         <v>31</v>
       </c>
       <c r="H15" t="n">
-        <v>490</v>
+        <v>422</v>
       </c>
       <c r="I15" t="n">
         <v>3</v>
@@ -2031,20 +1937,12 @@
         <v>-40</v>
       </c>
       <c r="M15" t="n">
-        <v>-509</v>
+        <v>-355</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2067,19 +1965,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1460</v>
+        <v>1600</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>9.77</v>
+        <v>4.92</v>
       </c>
       <c r="F16" t="n">
-        <v>1025</v>
+        <v>904</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>110</v>
       </c>
       <c r="H16" t="n">
-        <v>40</v>
+        <v>-36</v>
       </c>
       <c r="I16" t="n">
         <v>2</v>
@@ -2094,77 +1992,12 @@
         <v>65</v>
       </c>
       <c r="M16" t="n">
-        <v>-158</v>
+        <v>-81</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>1309</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>台達化</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>23.85</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>-10</v>
-      </c>
-      <c r="F17" t="n">
-        <v>8551</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-1398</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>9719</v>
-      </c>
-      <c r="M17" t="n">
-        <v>50152</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-97400</v>
-      </c>
-      <c r="O17" t="n">
-        <v>-3.4</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>

--- a/outputs/monitor_xlsx/20260408.xlsx
+++ b/outputs/monitor_xlsx/20260408.xlsx
@@ -544,10 +544,6 @@
           <t>+4.61%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>+4.79%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -596,10 +588,6 @@
           <t>+5.48%</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -622,10 +610,6 @@
           <t>-1.22%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -648,10 +632,6 @@
           <t>+1.98%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -674,10 +654,6 @@
           <t>-0.08%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -700,10 +676,6 @@
           <t>+6.34%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -726,10 +698,6 @@
           <t>-18.39%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -752,10 +720,6 @@
           <t>-16.41%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -773,7 +737,6 @@
           <t>1177.73億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>63.36億</t>
@@ -811,7 +774,6 @@
           <t>47.2億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>61.69億</t>
@@ -822,8 +784,6 @@
           <t>308.43億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -841,15 +801,11 @@
           <t>141.14%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>130.52%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -867,11 +823,6 @@
           <t>1583.61億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -889,15 +840,11 @@
           <t>10137口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>8317口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -915,7 +862,6 @@
           <t>-74.03億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>-9.15億</t>
@@ -1020,10 +966,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1145,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1179,6 +1122,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -2001,6 +1945,54 @@
         <is>
           <t>N/A</t>
         </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>539</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1809</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>402</v>
+      </c>
+      <c r="G17" t="n">
+        <v>912</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2462</v>
+      </c>
+      <c r="J17" t="n">
+        <v>28</v>
+      </c>
+      <c r="K17" t="n">
+        <v>10238</v>
+      </c>
+      <c r="L17" t="n">
+        <v>37712</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-21499</v>
+      </c>
+      <c r="N17" t="n">
+        <v>46.41</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260408.xlsx
+++ b/outputs/monitor_xlsx/20260408.xlsx
@@ -966,7 +966,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1243,7 +1242,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1251,26 +1250,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>79.2</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>5.18</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="7" t="n">
         <v>235675</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>96385</v>
       </c>
       <c r="H4" t="n">
-        <v>-145526</v>
+        <v>-49141</v>
       </c>
       <c r="I4" t="n">
         <v>-2116</v>
       </c>
       <c r="J4" t="n">
-        <v>4300</v>
+        <v>2184</v>
       </c>
       <c r="K4" t="n">
         <v>9607</v>
@@ -1279,11 +1278,14 @@
         <v>11328</v>
       </c>
       <c r="M4" t="n">
-        <v>54578</v>
+        <v>65906</v>
       </c>
       <c r="N4" t="n">
         <v>-4627719</v>
       </c>
+      <c r="O4" t="n">
+        <v>4.64</v>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1306,26 +1308,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6" t="n">
         <v>830</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>5.73</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="7" t="n">
         <v>1699</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>132</v>
       </c>
       <c r="H5" t="n">
-        <v>2498</v>
+        <v>2630</v>
       </c>
       <c r="I5" t="n">
         <v>-7</v>
       </c>
       <c r="J5" t="n">
-        <v>-948</v>
+        <v>-955</v>
       </c>
       <c r="K5" t="n">
         <v>13</v>
@@ -1334,11 +1336,14 @@
         <v>2637</v>
       </c>
       <c r="M5" t="n">
-        <v>10745</v>
+        <v>13382</v>
       </c>
       <c r="N5" t="n">
         <v>-78961</v>
       </c>
+      <c r="O5" t="n">
+        <v>-5.6</v>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1361,26 +1366,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>1665</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>9.9</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="7" t="n">
         <v>13400</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>3910</v>
       </c>
       <c r="H6" t="n">
-        <v>-3757</v>
+        <v>153</v>
       </c>
       <c r="I6" t="n">
         <v>-33</v>
       </c>
       <c r="J6" t="n">
-        <v>827</v>
+        <v>794</v>
       </c>
       <c r="K6" t="n">
         <v>390</v>
@@ -1389,11 +1394,14 @@
         <v>5641</v>
       </c>
       <c r="M6" t="n">
-        <v>21078</v>
+        <v>26719</v>
       </c>
       <c r="N6" t="n">
         <v>-649289</v>
       </c>
+      <c r="O6" t="n">
+        <v>14.87</v>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1416,26 +1424,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="6" t="n">
         <v>1950</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>4.84</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="7" t="n">
         <v>53813</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>18393</v>
       </c>
       <c r="H7" t="n">
-        <v>-17762</v>
+        <v>632</v>
       </c>
       <c r="I7" t="n">
         <v>452</v>
       </c>
       <c r="J7" t="n">
-        <v>2282</v>
+        <v>2734</v>
       </c>
       <c r="K7" t="n">
         <v>435</v>
@@ -1444,11 +1452,14 @@
         <v>26797</v>
       </c>
       <c r="M7" t="n">
-        <v>105559</v>
+        <v>132356</v>
       </c>
       <c r="N7" t="n">
         <v>-6483092</v>
       </c>
+      <c r="O7" t="n">
+        <v>5.43</v>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1471,26 +1482,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="6" t="n">
         <v>1710</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>5.88</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="6" t="n">
         <v>5374</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>-787</v>
       </c>
       <c r="H8" t="n">
-        <v>-1798</v>
+        <v>-2585</v>
       </c>
       <c r="I8" t="n">
         <v>337</v>
       </c>
       <c r="J8" t="n">
-        <v>1040</v>
+        <v>1377</v>
       </c>
       <c r="K8" t="n">
         <v>87</v>
@@ -1499,11 +1510,14 @@
         <v>1777</v>
       </c>
       <c r="M8" t="n">
-        <v>7927</v>
+        <v>9704</v>
       </c>
       <c r="N8" t="n">
         <v>-140279</v>
       </c>
+      <c r="O8" t="n">
+        <v>9.18</v>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1526,26 +1540,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="6" t="n">
         <v>1725</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>9.869999999999999</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="7" t="n">
         <v>2434</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>94</v>
       </c>
       <c r="H9" t="n">
-        <v>-616</v>
+        <v>-522</v>
       </c>
       <c r="I9" t="n">
         <v>-9</v>
       </c>
       <c r="J9" t="n">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="K9" t="n">
         <v>84</v>
@@ -1554,11 +1568,14 @@
         <v>2340</v>
       </c>
       <c r="M9" t="n">
-        <v>8475</v>
+        <v>10815</v>
       </c>
       <c r="N9" t="n">
         <v>-106305</v>
       </c>
+      <c r="O9" t="n">
+        <v>11.45</v>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1581,26 +1598,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="6" t="n">
         <v>3170</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>9.880000000000001</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="7" t="n">
         <v>2230</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>643</v>
       </c>
       <c r="H10" t="n">
-        <v>-49</v>
+        <v>593</v>
       </c>
       <c r="I10" t="n">
         <v>64</v>
       </c>
       <c r="J10" t="n">
-        <v>543</v>
+        <v>607</v>
       </c>
       <c r="K10" t="n">
         <v>114</v>
@@ -1609,11 +1626,14 @@
         <v>1965</v>
       </c>
       <c r="M10" t="n">
-        <v>7339</v>
+        <v>9304</v>
       </c>
       <c r="N10" t="n">
         <v>-89552</v>
       </c>
+      <c r="O10" t="n">
+        <v>15.11</v>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1636,26 +1656,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="6" t="n">
         <v>2165</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>3.34</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="6" t="n">
         <v>3062</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>-140</v>
       </c>
       <c r="H11" t="n">
-        <v>-14</v>
+        <v>-154</v>
       </c>
       <c r="I11" t="n">
         <v>48</v>
       </c>
       <c r="J11" t="n">
-        <v>198</v>
+        <v>246</v>
       </c>
       <c r="K11" t="n">
         <v>38</v>
@@ -1664,11 +1684,14 @@
         <v>3879</v>
       </c>
       <c r="M11" t="n">
-        <v>15398</v>
+        <v>19277</v>
       </c>
       <c r="N11" t="n">
         <v>-19405</v>
       </c>
+      <c r="O11" t="n">
+        <v>12.34</v>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1691,26 +1714,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="6" t="n">
         <v>7810</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="7" t="n">
         <v>205</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>74</v>
       </c>
       <c r="H12" t="n">
-        <v>219</v>
+        <v>293</v>
       </c>
       <c r="I12" t="n">
         <v>-10</v>
       </c>
       <c r="J12" t="n">
-        <v>-327</v>
+        <v>-337</v>
       </c>
       <c r="K12" t="n">
         <v>11</v>
@@ -1719,11 +1742,14 @@
         <v>318</v>
       </c>
       <c r="M12" t="n">
-        <v>1274</v>
+        <v>1592</v>
       </c>
       <c r="N12" t="n">
         <v>-8988</v>
       </c>
+      <c r="O12" t="n">
+        <v>8.970000000000001</v>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1746,26 +1772,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>2315</v>
+      <c r="D13" s="6" t="n">
+        <v>2365</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2730</v>
+        <v>2.16</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>2182</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>-189</v>
       </c>
       <c r="H13" t="n">
-        <v>-240</v>
+        <v>-429</v>
       </c>
       <c r="I13" t="n">
         <v>-150</v>
       </c>
       <c r="J13" t="n">
-        <v>1032</v>
+        <v>882</v>
       </c>
       <c r="K13" t="n">
         <v>-11</v>
@@ -1774,11 +1800,14 @@
         <v>-45</v>
       </c>
       <c r="M13" t="n">
-        <v>169</v>
+        <v>124</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1801,20 +1830,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>449.5</v>
+      <c r="D14" s="6" t="n">
+        <v>586</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3871</v>
+        <v>9.94</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>32773</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>-286</v>
       </c>
       <c r="H14" t="n">
-        <v>383</v>
+        <v>97</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1826,11 +1858,14 @@
         <v>-96</v>
       </c>
       <c r="M14" t="n">
-        <v>-962</v>
+        <v>-1058</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1853,26 +1888,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>974</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1350</v>
+      <c r="D15" s="7" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>6341</v>
       </c>
       <c r="G15" s="7" t="n">
         <v>31</v>
       </c>
       <c r="H15" t="n">
-        <v>422</v>
+        <v>453</v>
       </c>
       <c r="I15" t="n">
         <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
         <v>17</v>
@@ -1881,11 +1916,14 @@
         <v>-40</v>
       </c>
       <c r="M15" t="n">
-        <v>-355</v>
+        <v>-395</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1908,26 +1946,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1600</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="F16" t="n">
-        <v>904</v>
+      <c r="D16" s="7" t="n">
+        <v>1625</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>1168</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>110</v>
       </c>
       <c r="H16" t="n">
-        <v>-36</v>
+        <v>74</v>
       </c>
       <c r="I16" t="n">
         <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K16" t="n">
         <v>23</v>
@@ -1936,11 +1974,14 @@
         <v>65</v>
       </c>
       <c r="M16" t="n">
-        <v>-81</v>
+        <v>-16</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1958,41 +1999,46 @@
           <t>大量</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
         <v>539</v>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="E17" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" s="7" t="n">
         <v>1809</v>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="G17" s="7" t="n">
         <v>402</v>
       </c>
-      <c r="G17" t="n">
-        <v>912</v>
-      </c>
       <c r="H17" t="n">
+        <v>212</v>
+      </c>
+      <c r="I17" t="n">
         <v>0</v>
       </c>
-      <c r="I17" t="n">
-        <v>2462</v>
-      </c>
       <c r="J17" t="n">
+        <v>2795</v>
+      </c>
+      <c r="K17" t="n">
         <v>28</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>10238</v>
       </c>
-      <c r="L17" t="n">
-        <v>37712</v>
-      </c>
       <c r="M17" t="n">
+        <v>45481</v>
+      </c>
+      <c r="N17" t="n">
         <v>-21499</v>
       </c>
-      <c r="N17" t="n">
-        <v>46.41</v>
+      <c r="O17" t="n">
+        <v>44.11</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260408.xlsx
+++ b/outputs/monitor_xlsx/20260408.xlsx
@@ -1087,7 +1087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2041,6 +2041,165 @@
         <v>44.11</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1580</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="F18" t="n">
+        <v>14575</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>-81</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-4958</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-55</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-1688</v>
+      </c>
+      <c r="K18" t="n">
+        <v>227</v>
+      </c>
+      <c r="L18" t="n">
+        <v>6488</v>
+      </c>
+      <c r="M18" t="n">
+        <v>31761</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-400971</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-2.9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>620</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="F19" t="n">
+        <v>40382</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>6613</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1518</v>
+      </c>
+      <c r="I19" t="n">
+        <v>758</v>
+      </c>
+      <c r="J19" t="n">
+        <v>5576</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1046</v>
+      </c>
+      <c r="L19" t="n">
+        <v>35192</v>
+      </c>
+      <c r="M19" t="n">
+        <v>165905</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-393582</v>
+      </c>
+      <c r="O19" t="n">
+        <v>20.55</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>637</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="F20" t="n">
+        <v>32033</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-5477</v>
+      </c>
+      <c r="H20" t="n">
+        <v>371</v>
+      </c>
+      <c r="I20" t="n">
+        <v>344</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4300</v>
+      </c>
+      <c r="K20" t="n">
+        <v>790</v>
+      </c>
+      <c r="L20" t="n">
+        <v>9504</v>
+      </c>
+      <c r="M20" t="n">
+        <v>42124</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-160996</v>
+      </c>
+      <c r="O20" t="n">
+        <v>17.3</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
